--- a/registration_forms/032_mentorship_session_registration_form--registration_forms.xlsx
+++ b/registration_forms/032_mentorship_session_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1006,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1107,29 +1107,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mentor</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mentor</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mentor_info_choices</t>
+          <t>session_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mentor</t>
+          <t>one-on-one_session</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mentor</t>
+          <t>One-on-One Session</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>one-on-one_session</t>
+          <t>group_session</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>One-on-One Session</t>
+          <t>Group Session</t>
         </is>
       </c>
     </row>
@@ -1158,29 +1158,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>group_session</t>
+          <t>virtual_session</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Group Session</t>
+          <t>Virtual Session</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>session_type_choices</t>
+          <t>session_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>virtual_session</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Virtual Session</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1209,29 +1209,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>biweekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Biweekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>session_frequency_choices</t>
+          <t>submission_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>biweekly</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Biweekly</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1260,29 +1260,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>manual/auto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Manual/Auto</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submission_type_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>manual/auto</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manual/Auto</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1311,29 +1311,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>mentorship_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>mentorship</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Mentorship</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mentorship</t>
+          <t>comentorship</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mentorship</t>
+          <t>CoMentorship</t>
         </is>
       </c>
     </row>
@@ -1362,29 +1362,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>comentorship</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CoMentorship</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mentorship_type_choices</t>
+          <t>session_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1413,29 +1413,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>session_status_choices</t>
+          <t>participant_agreement_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Agreed</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Agreed</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1464,27 +1464,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>declined</t>
+          <t>no_agreement</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Declined</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>participant_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no_agreement</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>No Agreement</t>
         </is>
